--- a/Documentation/Documents/Blue Print/Documents - API/JSON Schema Restriction.xlsx
+++ b/Documentation/Documents/Blue Print/Documents - API/JSON Schema Restriction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>date</t>
   </si>
@@ -218,12 +218,16 @@
 .1234567, .2345678
 (+.1234567, -.2345678)</t>
   </si>
+  <si>
+    <t>"type": [ "string", "null" ],
+"contentMediaType": "application/json"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +251,13 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Narrow"/>
@@ -309,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -328,6 +339,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E21"/>
+  <dimension ref="B1:E22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
@@ -745,100 +762,110 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="2:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>30</v>
+    <row r="12" spans="2:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="2:5" ht="51" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="2:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" ht="51" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="2:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="2:5" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="2:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="2:5" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+    <row r="18" spans="2:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="E20" s="5"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
     </row>
